--- a/Python/dz2/work/output/pivot_status_by_species.xlsx
+++ b/Python/dz2/work/output/pivot_status_by_species.xlsx
@@ -14,12 +14,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>species_name</t>
   </si>
   <si>
     <t>В приюте</t>
+  </si>
+  <si>
+    <t>Готов к пристройству</t>
+  </si>
+  <si>
+    <t>Карантин</t>
   </si>
   <si>
     <t>На лечении</t>
@@ -389,10 +395,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -405,33 +411,51 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:6">
       <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2">
+        <v>7</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
+      <c r="D2">
+        <v>3</v>
+      </c>
+      <c r="E2">
         <v>4</v>
       </c>
-      <c r="B2">
+      <c r="F2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3">
+        <v>9</v>
+      </c>
+      <c r="C3">
+        <v>5</v>
+      </c>
+      <c r="D3">
         <v>1</v>
       </c>
-      <c r="C2">
-        <v>0</v>
-      </c>
-      <c r="D2">
+      <c r="E3">
+        <v>3</v>
+      </c>
+      <c r="F3">
         <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3">
-        <v>0</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
